--- a/ConsiderCourseChange_STU-01218332-65.xlsx
+++ b/ConsiderCourseChange_STU-01218332-65.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="300">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -37,7 +37,7 @@
     <t>รายชื่อนิสิต</t>
   </si>
   <si>
-    <t>สรุปทั้งหมด 45 คน สถานะ Drop ติด W  0 คน</t>
+    <t>สรุปทั้งหมด 46 คน สถานะ Drop ติด W  0 คน</t>
   </si>
   <si>
     <t>ลำดับที่</t>
@@ -70,6 +70,36 @@
     <t>1</t>
   </si>
   <si>
+    <t>6610553157</t>
+  </si>
+  <si>
+    <t>นายธีรพัส แก้วงาม</t>
+  </si>
+  <si>
+    <t>Mr. Theerapat KEAONGAM</t>
+  </si>
+  <si>
+    <t>วิศวกรรมศาสตร์</t>
+  </si>
+  <si>
+    <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
+  </si>
+  <si>
+    <t>E18</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>theerapat.ke@ku.th</t>
+  </si>
+  <si>
+    <t>theerapat.ke@live.ku.th</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>6610553165</t>
   </si>
   <si>
@@ -79,25 +109,13 @@
     <t>Miss Naphatson NUMAHAN</t>
   </si>
   <si>
-    <t>วิศวกรรมศาสตร์</t>
-  </si>
-  <si>
-    <t>วิศวกรรมสำรวจและสารสนเทศภูมิศาสตร์</t>
-  </si>
-  <si>
-    <t>E18</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>naphatson.nu@ku.th</t>
   </si>
   <si>
     <t>naphatson.nu@live.ku.th</t>
   </si>
   <si>
-    <t>2</t>
+    <t>3</t>
   </si>
   <si>
     <t>6610553173</t>
@@ -115,7 +133,7 @@
     <t>naraporn.ja@live.ku.th</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>6610553181</t>
@@ -133,7 +151,7 @@
     <t>bunyamin.m@live.ku.th</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>6610553203</t>
@@ -151,7 +169,7 @@
     <t>panyanan.t@live.ku.th</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>6610553220</t>
@@ -169,7 +187,7 @@
     <t>phinyada.sr@live.ku.th</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>6610553238</t>
@@ -187,7 +205,7 @@
     <t>purin.m@live.ku.th</t>
   </si>
   <si>
-    <t>7</t>
+    <t>8</t>
   </si>
   <si>
     <t>6610553254</t>
@@ -205,7 +223,7 @@
     <t>ratchanon.sakh@live.ku.th</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>6610553262</t>
@@ -223,7 +241,7 @@
     <t>worapon.pl@live.ku.th</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>6610553271</t>
@@ -241,7 +259,7 @@
     <t>suphanat.chan@live.ku.th</t>
   </si>
   <si>
-    <t>10</t>
+    <t>11</t>
   </si>
   <si>
     <t>6610553289</t>
@@ -259,7 +277,7 @@
     <t>settakamol.wa@live.ku.th</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>6610553327</t>
@@ -277,7 +295,7 @@
     <t>arisara.len@live.ku.th</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>6610554153</t>
@@ -295,7 +313,7 @@
     <t>pattarapon.ditt@live.ku.th</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>6610554161</t>
@@ -313,7 +331,7 @@
     <t>pakin.saen@live.ku.th</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>6710552942</t>
@@ -331,7 +349,7 @@
     <t>kanol.s@live.ku.th</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>6710552951</t>
@@ -349,7 +367,7 @@
     <t>kamonnit.t@live.ku.th</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
   </si>
   <si>
     <t>6710552969</t>
@@ -367,7 +385,7 @@
     <t>krisskon.s@live.ku.th</t>
   </si>
   <si>
-    <t>17</t>
+    <t>18</t>
   </si>
   <si>
     <t>6710552977</t>
@@ -385,7 +403,7 @@
     <t>kantiwat.ta@live.ku.th</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>6710552985</t>
@@ -403,7 +421,7 @@
     <t>kasemchoke.na@live.ku.th</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>6710552993</t>
@@ -421,7 +439,7 @@
     <t>jakkarin.in@live.ku.th</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>6710553001</t>
@@ -439,7 +457,7 @@
     <t>chanchao.t@live.ku.th</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>6710553027</t>
@@ -457,7 +475,7 @@
     <t>tikamporn.tr@live.ku.th</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>6710553035</t>
@@ -475,7 +493,7 @@
     <t>napapach.bu@live.ku.th</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>6710553051</t>
@@ -493,7 +511,7 @@
     <t>tanatud.m@live.ku.th</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>6710553078</t>
@@ -511,7 +529,7 @@
     <t>thanaphum.l@live.ku.th</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>6710553086</t>
@@ -529,7 +547,7 @@
     <t>thanakon.r@live.ku.th</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>6710553094</t>
@@ -547,7 +565,7 @@
     <t>thammakorn.c@live.ku.th</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>6710553108</t>
@@ -565,7 +583,7 @@
     <t>thattawan.y@live.ku.th</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>6710553124</t>
@@ -583,7 +601,7 @@
     <t>nonthakorn.j@live.ku.th</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>6710553141</t>
@@ -601,7 +619,7 @@
     <t>naputrapee.a@live.ku.th</t>
   </si>
   <si>
-    <t>30</t>
+    <t>31</t>
   </si>
   <si>
     <t>6710553167</t>
@@ -619,7 +637,7 @@
     <t>pichayut.l@live.ku.th</t>
   </si>
   <si>
-    <t>31</t>
+    <t>32</t>
   </si>
   <si>
     <t>6710553191</t>
@@ -637,7 +655,7 @@
     <t>pakhawat.p@live.ku.th</t>
   </si>
   <si>
-    <t>32</t>
+    <t>33</t>
   </si>
   <si>
     <t>6710553205</t>
@@ -655,7 +673,7 @@
     <t>phakkaphon.l@live.ku.th</t>
   </si>
   <si>
-    <t>33</t>
+    <t>34</t>
   </si>
   <si>
     <t>6710553213</t>
@@ -673,7 +691,7 @@
     <t>pakkapon.i@live.ku.th</t>
   </si>
   <si>
-    <t>34</t>
+    <t>35</t>
   </si>
   <si>
     <t>6710553264</t>
@@ -691,7 +709,7 @@
     <t>yuttana.sukku@live.ku.th</t>
   </si>
   <si>
-    <t>35</t>
+    <t>36</t>
   </si>
   <si>
     <t>6710553272</t>
@@ -709,7 +727,7 @@
     <t>rapeepat.mo@live.ku.th</t>
   </si>
   <si>
-    <t>36</t>
+    <t>37</t>
   </si>
   <si>
     <t>6710553281</t>
@@ -727,7 +745,7 @@
     <t>veerapat.d@live.ku.th</t>
   </si>
   <si>
-    <t>37</t>
+    <t>38</t>
   </si>
   <si>
     <t>6710553299</t>
@@ -745,7 +763,7 @@
     <t>savita.cha@live.ku.th</t>
   </si>
   <si>
-    <t>38</t>
+    <t>39</t>
   </si>
   <si>
     <t>6710553329</t>
@@ -763,7 +781,7 @@
     <t>sorasak.cot@live.ku.th</t>
   </si>
   <si>
-    <t>39</t>
+    <t>40</t>
   </si>
   <si>
     <t>6710553337</t>
@@ -781,7 +799,7 @@
     <t>sarawut.ya@live.ku.th</t>
   </si>
   <si>
-    <t>40</t>
+    <t>41</t>
   </si>
   <si>
     <t>6710553345</t>
@@ -799,7 +817,7 @@
     <t>sitthichailoet.s@live.ku.th</t>
   </si>
   <si>
-    <t>41</t>
+    <t>42</t>
   </si>
   <si>
     <t>6710553353</t>
@@ -817,7 +835,7 @@
     <t>sutichode.b@live.ku.th</t>
   </si>
   <si>
-    <t>42</t>
+    <t>43</t>
   </si>
   <si>
     <t>6710553361</t>
@@ -835,7 +853,7 @@
     <t>sumath.o@live.ku.th</t>
   </si>
   <si>
-    <t>43</t>
+    <t>44</t>
   </si>
   <si>
     <t>6710553370</t>
@@ -853,7 +871,7 @@
     <t>aussanee.ko@live.ku.th</t>
   </si>
   <si>
-    <t>44</t>
+    <t>45</t>
   </si>
   <si>
     <t>6710553388</t>
@@ -871,7 +889,7 @@
     <t>atitaya.thai@live.ku.th</t>
   </si>
   <si>
-    <t>45</t>
+    <t>46</t>
   </si>
   <si>
     <t>6710553396</t>
@@ -889,7 +907,7 @@
     <t>araya.sansu@live.ku.th</t>
   </si>
   <si>
-    <t>วันเวลาที่พิมพ์รายงาน 29/06/2569 13:39:12</t>
+    <t>วันเวลาที่พิมพ์รายงาน 10/07/2569 00:51:06</t>
   </si>
   <si>
     <t>ผู้พิมพ์รายงาน ผู้ช่วยศาสตราจารย์อนุเผ่า อบแพทย์</t>
@@ -1017,7 +1035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K55"/>
+  <dimension ref="A1:K56"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
@@ -2549,12 +2567,44 @@
         <v>291</v>
       </c>
     </row>
-    <row r="55" spans="2:7">
-      <c r="B55" s="1" t="s">
+    <row r="53" spans="2:11">
+      <c r="B53" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="C53" s="5" t="s">
         <v>293</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="56" spans="2:7">
+      <c r="B56" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>299</v>
       </c>
     </row>
   </sheetData>
